--- a/FLORES DE ESTRADA/Mayo/RESUMEN-MAYO-ESTRADA.xlsx
+++ b/FLORES DE ESTRADA/Mayo/RESUMEN-MAYO-ESTRADA.xlsx
@@ -5,18 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\FLORES DE ESTRADA\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3351155F-3A49-4491-9142-DEB608ADBCFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A23BAE0C-CC29-4A6B-B71E-3827556D7DE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$1:$H$60</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$1:$H$56</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="45">
   <si>
     <t>Domicilio:</t>
   </si>
@@ -138,21 +138,9 @@
     <t xml:space="preserve">PREVISION ORDINARIA </t>
   </si>
   <si>
-    <t xml:space="preserve">Jardineria </t>
-  </si>
-  <si>
     <t>AUMENTARON LOS HONORARIOS EN ABRI 2025</t>
   </si>
   <si>
-    <t>ASCENSORES Premec S.R.L. - Cableado de cirtuito de conexión entre cabina y tablero de mando para habilitacion de barrera de puerto por falla - Debido al corte del circuito del cableado de linea 24v - Materiales y mano de obra</t>
-  </si>
-  <si>
-    <t>Doartero - Mano de obra cambio de linga</t>
-  </si>
-  <si>
-    <t>PERIODO: MAYO - Vto. 16/06/2025</t>
-  </si>
-  <si>
     <t>AYSA - MAYO 2025</t>
   </si>
   <si>
@@ -168,7 +156,13 @@
     <t>Egresos gastos del mes - MAYO EXTRAORDINARIO</t>
   </si>
   <si>
-    <t>CAJA NO REAL, YA QUE DE ESTE FONDO SE PAGA EDESUR DE LAS UNIDADES FUNCIONALES ATRASADAS. A PARTIR DE LA LIQUIDACION DE MAYO 2025, QUIEN SE ATRASE CON EDESUR TENDRA PUNITORIOS.</t>
+    <t>PERIODO: MAYO - Vto. 10/06/2025</t>
+  </si>
+  <si>
+    <t>Electrocerradura - comprada por Alcoleas Christian e instalacion</t>
+  </si>
+  <si>
+    <t>CAJA NO REAL, YA QUE DE ESTE FONDO SE PAGA EDESUR DE LAS UNIDADES FUNCIONALES ATRASADAS. QUIEN SE ATRASE CON EDESUR TENDRA PUNITORIOS.</t>
   </si>
 </sst>
 </file>
@@ -176,12 +170,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -259,21 +253,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -499,13 +478,13 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -513,7 +492,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="6" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -523,28 +502,28 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="7" fillId="5" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="8" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="6" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="5" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="8" fontId="7" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="4" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="8" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="7" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
@@ -556,92 +535,64 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="6" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="44" fontId="11" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="44" fontId="11" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="11" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="6" fontId="5" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="5" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="12" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="12" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -979,16 +930,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K59"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K55"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="7" max="7" width="11.6640625" customWidth="1"/>
-    <col min="8" max="8" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" customWidth="1"/>
+    <col min="8" max="8" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="36"/>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
@@ -998,7 +949,7 @@
       <c r="G1" s="37"/>
       <c r="H1" s="38"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="34"/>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
@@ -1012,7 +963,7 @@
       <c r="G2" s="11"/>
       <c r="H2" s="7"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="34"/>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
@@ -1026,7 +977,7 @@
       <c r="G3" s="11"/>
       <c r="H3" s="7"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="34"/>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -1040,7 +991,7 @@
       <c r="G4" s="11"/>
       <c r="H4" s="7"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="34"/>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -1052,7 +1003,7 @@
       <c r="G5" s="11"/>
       <c r="H5" s="7"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="34"/>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -1062,7 +1013,7 @@
       <c r="G6" s="11"/>
       <c r="H6" s="7"/>
     </row>
-    <row r="7" spans="1:8" ht="18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A7" s="41" t="s">
         <v>5</v>
       </c>
@@ -1070,13 +1021,13 @@
       <c r="C7" s="42"/>
       <c r="D7" s="42"/>
       <c r="E7" s="42" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F7" s="42"/>
       <c r="G7" s="43"/>
       <c r="H7" s="44"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="36"/>
       <c r="B8" s="37"/>
       <c r="C8" s="37"/>
@@ -1086,7 +1037,7 @@
       <c r="G8" s="37"/>
       <c r="H8" s="38"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="34" t="s">
         <v>6</v>
       </c>
@@ -1100,7 +1051,7 @@
       <c r="G9" s="11"/>
       <c r="H9" s="7"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="34" t="s">
         <v>8</v>
       </c>
@@ -1114,7 +1065,7 @@
       <c r="G10" s="11"/>
       <c r="H10" s="7"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -1124,19 +1075,19 @@
       <c r="G11" s="5"/>
       <c r="H11" s="6"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="75" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="75"/>
-      <c r="C12" s="75"/>
-      <c r="D12" s="75"/>
-      <c r="E12" s="75"/>
-      <c r="F12" s="75"/>
-      <c r="G12" s="75"/>
-      <c r="H12" s="75"/>
-    </row>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="64"/>
+      <c r="C12" s="64"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="64"/>
+      <c r="H12" s="64"/>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="34" t="s">
         <v>28</v>
       </c>
@@ -1146,54 +1097,54 @@
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="11"/>
-      <c r="H13" s="57">
+      <c r="H13" s="48">
         <v>194000</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="83" t="s">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="68" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="84"/>
-      <c r="C14" s="84"/>
-      <c r="D14" s="84"/>
-      <c r="E14" s="84"/>
-      <c r="F14" s="84"/>
-      <c r="G14" s="84"/>
-      <c r="H14" s="89">
+      <c r="B14" s="69"/>
+      <c r="C14" s="69"/>
+      <c r="D14" s="69"/>
+      <c r="E14" s="69"/>
+      <c r="F14" s="69"/>
+      <c r="G14" s="69"/>
+      <c r="H14" s="48">
         <v>3567.21</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="58" t="s">
+    <row r="15" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="59"/>
-      <c r="C15" s="59"/>
-      <c r="D15" s="59"/>
-      <c r="E15" s="59"/>
-      <c r="F15" s="59"/>
-      <c r="G15" s="59"/>
-      <c r="H15" s="60">
+      <c r="B15" s="50"/>
+      <c r="C15" s="50"/>
+      <c r="D15" s="50"/>
+      <c r="E15" s="50"/>
+      <c r="F15" s="50"/>
+      <c r="G15" s="50"/>
+      <c r="H15" s="51">
         <f>SUM(H13:H14)</f>
         <v>197567.21</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="76" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="77"/>
-      <c r="C16" s="77"/>
-      <c r="D16" s="77"/>
-      <c r="E16" s="77"/>
-      <c r="F16" s="77"/>
-      <c r="G16" s="77"/>
-      <c r="H16" s="78"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B16" s="66"/>
+      <c r="C16" s="66"/>
+      <c r="D16" s="66"/>
+      <c r="E16" s="66"/>
+      <c r="F16" s="66"/>
+      <c r="G16" s="66"/>
+      <c r="H16" s="67"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="34" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -1201,52 +1152,52 @@
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
       <c r="G17" s="11"/>
-      <c r="H17" s="90">
+      <c r="H17" s="52">
         <v>29660.67</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="58" t="s">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="59"/>
-      <c r="C18" s="59"/>
-      <c r="D18" s="59"/>
-      <c r="E18" s="59"/>
-      <c r="F18" s="59"/>
-      <c r="G18" s="59"/>
-      <c r="H18" s="62">
+      <c r="B18" s="50"/>
+      <c r="C18" s="50"/>
+      <c r="D18" s="50"/>
+      <c r="E18" s="50"/>
+      <c r="F18" s="50"/>
+      <c r="G18" s="50"/>
+      <c r="H18" s="53">
         <f>SUM(H17:H17)</f>
         <v>29660.67</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="76" t="s">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="77"/>
-      <c r="C19" s="77"/>
-      <c r="D19" s="77"/>
-      <c r="E19" s="77"/>
-      <c r="F19" s="77"/>
-      <c r="G19" s="77"/>
-      <c r="H19" s="78"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="63" t="s">
+      <c r="B19" s="66"/>
+      <c r="C19" s="66"/>
+      <c r="D19" s="66"/>
+      <c r="E19" s="66"/>
+      <c r="F19" s="66"/>
+      <c r="G19" s="66"/>
+      <c r="H19" s="67"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="64"/>
-      <c r="C20" s="64"/>
-      <c r="D20" s="64"/>
-      <c r="E20" s="64"/>
-      <c r="F20" s="64"/>
-      <c r="G20" s="64"/>
-      <c r="H20" s="65">
+      <c r="B20" s="55"/>
+      <c r="C20" s="55"/>
+      <c r="D20" s="55"/>
+      <c r="E20" s="55"/>
+      <c r="F20" s="55"/>
+      <c r="G20" s="55"/>
+      <c r="H20" s="56">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="34" t="s">
         <v>33</v>
       </c>
@@ -1256,11 +1207,11 @@
       <c r="E21" s="11"/>
       <c r="F21" s="11"/>
       <c r="G21" s="11"/>
-      <c r="H21" s="61">
+      <c r="H21" s="52">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="34" t="s">
         <v>9</v>
       </c>
@@ -1270,473 +1221,444 @@
       <c r="E22" s="11"/>
       <c r="F22" s="11"/>
       <c r="G22" s="11"/>
-      <c r="H22" s="66">
+      <c r="H22" s="57">
         <f>SUM(H20:H21)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="75" t="s">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="75"/>
-      <c r="C23" s="75"/>
-      <c r="D23" s="75"/>
-      <c r="E23" s="75"/>
-      <c r="F23" s="75"/>
-      <c r="G23" s="75"/>
-      <c r="H23" s="75"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="85" t="s">
-        <v>42</v>
-      </c>
-      <c r="B24" s="86"/>
-      <c r="C24" s="86"/>
-      <c r="D24" s="86"/>
-      <c r="E24" s="86"/>
-      <c r="F24" s="86"/>
-      <c r="G24" s="86"/>
-      <c r="H24" s="61">
+      <c r="B23" s="64"/>
+      <c r="C23" s="64"/>
+      <c r="D23" s="64"/>
+      <c r="E23" s="64"/>
+      <c r="F23" s="64"/>
+      <c r="G23" s="64"/>
+      <c r="H23" s="64"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="70" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="71"/>
+      <c r="C24" s="71"/>
+      <c r="D24" s="71"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="71"/>
+      <c r="G24" s="71"/>
+      <c r="H24" s="52">
         <v>91930.94</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="68" t="s">
+    <row r="25" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="72" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="73"/>
+      <c r="C25" s="73"/>
+      <c r="D25" s="73"/>
+      <c r="E25" s="73"/>
+      <c r="F25" s="73"/>
+      <c r="G25" s="73"/>
+      <c r="H25" s="52">
+        <f>167000+70000</f>
+        <v>237000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26" s="50"/>
+      <c r="C26" s="50"/>
+      <c r="D26" s="50"/>
+      <c r="E26" s="50"/>
+      <c r="F26" s="50"/>
+      <c r="G26" s="50"/>
+      <c r="H26" s="53">
+        <f>SUM(H24:H25)</f>
+        <v>328930.94</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="B27" s="66"/>
+      <c r="C27" s="66"/>
+      <c r="D27" s="66"/>
+      <c r="E27" s="66"/>
+      <c r="F27" s="66"/>
+      <c r="G27" s="66"/>
+      <c r="H27" s="67"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="32"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="49" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="67"/>
-      <c r="C25" s="67"/>
-      <c r="D25" s="67"/>
-      <c r="E25" s="67"/>
-      <c r="F25" s="67"/>
-      <c r="G25" s="67"/>
-      <c r="H25" s="61">
-        <v>40000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="87" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="88"/>
-      <c r="C26" s="88"/>
-      <c r="D26" s="88"/>
-      <c r="E26" s="88"/>
-      <c r="F26" s="88"/>
-      <c r="G26" s="88"/>
-      <c r="H26" s="61">
-        <v>730000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="34" t="s">
+      <c r="B29" s="50"/>
+      <c r="C29" s="50"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="50"/>
+      <c r="F29" s="50"/>
+      <c r="G29" s="50"/>
+      <c r="H29" s="74">
+        <v>139770.16</v>
+      </c>
+      <c r="I29" s="32"/>
+      <c r="K29" t="s">
         <v>36</v>
       </c>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="61">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="49" t="s">
-        <v>12</v>
-      </c>
-      <c r="B28" s="50"/>
-      <c r="C28" s="50"/>
-      <c r="D28" s="50"/>
-      <c r="E28" s="50"/>
-      <c r="F28" s="50"/>
-      <c r="G28" s="50"/>
-      <c r="H28" s="53">
-        <f>SUM(H24:H27)</f>
-        <v>891930.94</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="48"/>
-      <c r="H29" s="54"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="79" t="s">
-        <v>22</v>
-      </c>
-      <c r="B30" s="80"/>
-      <c r="C30" s="80"/>
-      <c r="D30" s="80"/>
-      <c r="E30" s="80"/>
-      <c r="F30" s="80"/>
-      <c r="G30" s="80"/>
-      <c r="H30" s="81"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="C31" t="s">
-        <v>14</v>
-      </c>
-      <c r="E31" t="s">
-        <v>26</v>
-      </c>
-      <c r="H31" s="54"/>
-      <c r="I31" s="32"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A32" s="49" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" s="50"/>
-      <c r="C32" s="50"/>
-      <c r="D32" s="50"/>
-      <c r="E32" s="50"/>
-      <c r="F32" s="50"/>
-      <c r="G32" s="50"/>
-      <c r="H32" s="55">
-        <v>139770.16</v>
-      </c>
-      <c r="I32" s="32"/>
-      <c r="K32" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A33" s="48"/>
-      <c r="H33" s="56"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A34" s="82" t="s">
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="64" t="s">
         <v>23</v>
       </c>
-      <c r="B34" s="82"/>
-      <c r="C34" s="82"/>
-      <c r="D34" s="82"/>
-      <c r="E34" s="82"/>
-      <c r="F34" s="82"/>
-      <c r="G34" s="82"/>
-      <c r="H34" s="82"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" s="51" t="s">
+      <c r="B30" s="64"/>
+      <c r="C30" s="64"/>
+      <c r="D30" s="64"/>
+      <c r="E30" s="64"/>
+      <c r="F30" s="64"/>
+      <c r="G30" s="64"/>
+      <c r="H30" s="64"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B35" s="52"/>
-      <c r="C35" s="52"/>
-      <c r="D35" s="52"/>
-      <c r="E35" s="52"/>
-      <c r="F35" s="52"/>
-      <c r="G35" s="52"/>
-      <c r="H35" s="69">
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="58">
         <v>49773</v>
       </c>
     </row>
-    <row r="36" spans="1:10" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="8" t="s">
+    <row r="32" spans="1:11" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="10">
-        <f>H35+H32+H28+H22+H18+H15</f>
-        <v>1308701.9799999997</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="21" t="s">
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="10">
+        <f>H31+H29+H26+H22+H18+H15</f>
+        <v>745701.98</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="B37" s="21"/>
-      <c r="C37" s="21"/>
-      <c r="D37" s="21"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="21"/>
-      <c r="G37" s="21"/>
-      <c r="H37" s="22"/>
-      <c r="I37" s="33"/>
-      <c r="J37" s="33"/>
-    </row>
-    <row r="38" spans="1:10" s="3" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="21" t="s">
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="22">
+        <v>500000</v>
+      </c>
+      <c r="I33" s="33"/>
+      <c r="J33" s="33"/>
+    </row>
+    <row r="34" spans="1:10" s="3" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B38" s="21"/>
-      <c r="C38" s="21"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="21"/>
-      <c r="G38" s="21"/>
-      <c r="H38" s="22">
-        <f>H36+H37</f>
-        <v>1308701.9799999997</v>
-      </c>
-      <c r="I38" s="35"/>
-    </row>
-    <row r="39" spans="1:10" s="3" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="23"/>
-      <c r="B39" s="24"/>
-      <c r="C39" s="24"/>
-      <c r="D39" s="24"/>
-      <c r="E39" s="24"/>
-      <c r="F39" s="24"/>
-      <c r="G39" s="24"/>
-      <c r="H39" s="25"/>
-    </row>
-    <row r="40" spans="1:10" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="26"/>
-      <c r="B40" s="26"/>
-      <c r="C40" s="26"/>
-      <c r="D40" s="26"/>
-      <c r="E40" s="26"/>
-      <c r="F40" s="26"/>
-      <c r="G40" s="26"/>
-      <c r="H40" s="27"/>
-    </row>
-    <row r="41" spans="1:10" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="26"/>
-      <c r="B41" s="26"/>
-      <c r="C41" s="26"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="26"/>
-      <c r="G41" s="26"/>
-      <c r="H41" s="28"/>
-    </row>
-    <row r="42" spans="1:10" s="1" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="45" t="s">
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="21"/>
+      <c r="H34" s="22">
+        <f>H32+H33</f>
+        <v>1245701.98</v>
+      </c>
+      <c r="I34" s="35"/>
+    </row>
+    <row r="35" spans="1:10" s="3" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="23"/>
+      <c r="B35" s="24"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="24"/>
+      <c r="H35" s="25"/>
+    </row>
+    <row r="36" spans="1:10" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="26"/>
+      <c r="B36" s="26"/>
+      <c r="C36" s="26"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="26"/>
+      <c r="H36" s="27"/>
+    </row>
+    <row r="37" spans="1:10" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="26"/>
+      <c r="B37" s="26"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="26"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="26"/>
+      <c r="G37" s="26"/>
+      <c r="H37" s="28"/>
+    </row>
+    <row r="38" spans="1:10" s="1" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B42" s="46"/>
-      <c r="C42" s="46"/>
-      <c r="D42" s="46"/>
-      <c r="E42" s="46"/>
-      <c r="F42" s="46"/>
-      <c r="G42" s="46"/>
-      <c r="H42" s="47">
-        <f>SUM(H40:H41)</f>
+      <c r="B38" s="46"/>
+      <c r="C38" s="46"/>
+      <c r="D38" s="46"/>
+      <c r="E38" s="46"/>
+      <c r="F38" s="46"/>
+      <c r="G38" s="46"/>
+      <c r="H38" s="47">
+        <f>SUM(H36:H37)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="71" t="s">
+    <row r="39" spans="1:10" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="B43" s="71"/>
-      <c r="C43" s="71"/>
-      <c r="D43" s="71"/>
-      <c r="E43" s="71"/>
-      <c r="F43" s="71"/>
-      <c r="G43" s="71"/>
-      <c r="H43" s="71"/>
-    </row>
-    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="71"/>
-      <c r="B44" s="71"/>
-      <c r="C44" s="71"/>
-      <c r="D44" s="71"/>
-      <c r="E44" s="71"/>
-      <c r="F44" s="71"/>
-      <c r="G44" s="71"/>
-      <c r="H44" s="71"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A45" s="11"/>
-      <c r="B45" s="11"/>
-      <c r="C45" s="11"/>
-      <c r="D45" s="11"/>
-      <c r="E45" s="11"/>
-      <c r="F45" s="11"/>
-      <c r="G45" s="11"/>
-      <c r="H45" s="11"/>
-    </row>
-    <row r="46" spans="1:10" ht="18" x14ac:dyDescent="0.35">
-      <c r="A46" s="72"/>
-      <c r="B46" s="73"/>
-      <c r="C46" s="73"/>
-      <c r="D46" s="73"/>
-      <c r="E46" s="73"/>
-      <c r="F46" s="73"/>
-      <c r="G46" s="73"/>
-      <c r="H46" s="74"/>
-      <c r="J46" s="2"/>
-    </row>
-    <row r="47" spans="1:10" ht="18" x14ac:dyDescent="0.35">
-      <c r="A47" s="12" t="s">
+      <c r="B39" s="60"/>
+      <c r="C39" s="60"/>
+      <c r="D39" s="60"/>
+      <c r="E39" s="60"/>
+      <c r="F39" s="60"/>
+      <c r="G39" s="60"/>
+      <c r="H39" s="60"/>
+    </row>
+    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="60"/>
+      <c r="B40" s="60"/>
+      <c r="C40" s="60"/>
+      <c r="D40" s="60"/>
+      <c r="E40" s="60"/>
+      <c r="F40" s="60"/>
+      <c r="G40" s="60"/>
+      <c r="H40" s="60"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="11"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11"/>
+    </row>
+    <row r="42" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A42" s="61"/>
+      <c r="B42" s="62"/>
+      <c r="C42" s="62"/>
+      <c r="D42" s="62"/>
+      <c r="E42" s="62"/>
+      <c r="F42" s="62"/>
+      <c r="G42" s="62"/>
+      <c r="H42" s="63"/>
+      <c r="J42" s="2"/>
+    </row>
+    <row r="43" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A43" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B47" s="13"/>
-      <c r="C47" s="13"/>
-      <c r="D47" s="13"/>
-      <c r="E47" s="13"/>
-      <c r="F47" s="13"/>
-      <c r="G47" s="13"/>
-      <c r="H47" s="20">
-        <v>1971617.0914498565</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A48" s="14" t="s">
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
+      <c r="H43" s="20">
+        <v>1495376.39</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="B48" s="15"/>
-      <c r="C48" s="15"/>
-      <c r="D48" s="15"/>
-      <c r="E48" s="15"/>
-      <c r="F48" s="15"/>
-      <c r="G48" s="15"/>
-      <c r="H48" s="30">
-        <v>831828.22012076806</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" s="14" t="s">
+      <c r="B44" s="15"/>
+      <c r="C44" s="15"/>
+      <c r="D44" s="15"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="15"/>
+      <c r="G44" s="15"/>
+      <c r="H44" s="30">
+        <v>1027656.6683125072</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="B49" s="15"/>
-      <c r="C49" s="15"/>
-      <c r="D49" s="15"/>
-      <c r="E49" s="15"/>
-      <c r="F49" s="15"/>
-      <c r="G49" s="15"/>
-      <c r="H49" s="16"/>
-      <c r="I49" s="31"/>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" s="14" t="s">
+      <c r="B45" s="15"/>
+      <c r="C45" s="15"/>
+      <c r="D45" s="15"/>
+      <c r="E45" s="15"/>
+      <c r="F45" s="15"/>
+      <c r="G45" s="15"/>
+      <c r="H45" s="16"/>
+      <c r="I45" s="31"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="15"/>
+      <c r="C46" s="15"/>
+      <c r="D46" s="15"/>
+      <c r="E46" s="15"/>
+      <c r="F46" s="15"/>
+      <c r="G46" s="15"/>
+      <c r="H46" s="17">
+        <f>-( H32 )</f>
+        <v>-745701.98</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="15"/>
+      <c r="C47" s="15"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="15"/>
+      <c r="F47" s="15"/>
+      <c r="G47" s="15"/>
+      <c r="H47" s="17"/>
+    </row>
+    <row r="48" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A48" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B48" s="19"/>
+      <c r="C48" s="19"/>
+      <c r="D48" s="19"/>
+      <c r="E48" s="19"/>
+      <c r="F48" s="19"/>
+      <c r="G48" s="19"/>
+      <c r="H48" s="29">
+        <f>SUM(H43:H47)</f>
+        <v>1777331.0783125074</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="11"/>
+      <c r="B49" s="11"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="11"/>
+      <c r="F49" s="11"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="11"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="11"/>
+      <c r="B50" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="B50" s="15"/>
-      <c r="C50" s="15"/>
-      <c r="D50" s="15"/>
-      <c r="E50" s="15"/>
-      <c r="F50" s="15"/>
-      <c r="G50" s="15"/>
-      <c r="H50" s="17">
-        <f>-( H36 )</f>
-        <v>-1308701.9799999997</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" s="15"/>
-      <c r="C51" s="15"/>
-      <c r="D51" s="15"/>
-      <c r="E51" s="15"/>
-      <c r="F51" s="15"/>
-      <c r="G51" s="15"/>
-      <c r="H51" s="17"/>
-    </row>
-    <row r="52" spans="1:9" ht="18" x14ac:dyDescent="0.35">
-      <c r="A52" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B52" s="19"/>
-      <c r="C52" s="19"/>
-      <c r="D52" s="19"/>
-      <c r="E52" s="19"/>
-      <c r="F52" s="19"/>
-      <c r="G52" s="19"/>
-      <c r="H52" s="29">
-        <f>SUM(H47:H51)</f>
-        <v>1494743.3315706251</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C50" s="59"/>
+      <c r="D50" s="59"/>
+      <c r="E50" s="59"/>
+      <c r="F50" s="59"/>
+      <c r="G50" s="59"/>
+      <c r="H50" s="11"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="11"/>
+      <c r="B51" s="59"/>
+      <c r="C51" s="59"/>
+      <c r="D51" s="59"/>
+      <c r="E51" s="59"/>
+      <c r="F51" s="59"/>
+      <c r="G51" s="59"/>
+      <c r="H51" s="11"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="11"/>
+      <c r="B52" s="59"/>
+      <c r="C52" s="59"/>
+      <c r="D52" s="59"/>
+      <c r="E52" s="59"/>
+      <c r="F52" s="59"/>
+      <c r="G52" s="59"/>
+      <c r="H52" s="11"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="11"/>
-      <c r="B53" s="11"/>
-      <c r="C53" s="11"/>
-      <c r="D53" s="11"/>
-      <c r="E53" s="11"/>
-      <c r="F53" s="11"/>
-      <c r="G53" s="11"/>
+      <c r="B53" s="59"/>
+      <c r="C53" s="59"/>
+      <c r="D53" s="59"/>
+      <c r="E53" s="59"/>
+      <c r="F53" s="59"/>
+      <c r="G53" s="59"/>
       <c r="H53" s="11"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="11"/>
-      <c r="B54" s="70" t="s">
-        <v>46</v>
-      </c>
-      <c r="C54" s="70"/>
-      <c r="D54" s="70"/>
-      <c r="E54" s="70"/>
-      <c r="F54" s="70"/>
-      <c r="G54" s="70"/>
+      <c r="B54" s="59"/>
+      <c r="C54" s="59"/>
+      <c r="D54" s="59"/>
+      <c r="E54" s="59"/>
+      <c r="F54" s="59"/>
+      <c r="G54" s="59"/>
       <c r="H54" s="11"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="11"/>
-      <c r="B55" s="70"/>
-      <c r="C55" s="70"/>
-      <c r="D55" s="70"/>
-      <c r="E55" s="70"/>
-      <c r="F55" s="70"/>
-      <c r="G55" s="70"/>
+      <c r="B55" s="59"/>
+      <c r="C55" s="59"/>
+      <c r="D55" s="59"/>
+      <c r="E55" s="59"/>
+      <c r="F55" s="59"/>
+      <c r="G55" s="59"/>
       <c r="H55" s="11"/>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A56" s="11"/>
-      <c r="B56" s="70"/>
-      <c r="C56" s="70"/>
-      <c r="D56" s="70"/>
-      <c r="E56" s="70"/>
-      <c r="F56" s="70"/>
-      <c r="G56" s="70"/>
-      <c r="H56" s="11"/>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A57" s="11"/>
-      <c r="B57" s="70"/>
-      <c r="C57" s="70"/>
-      <c r="D57" s="70"/>
-      <c r="E57" s="70"/>
-      <c r="F57" s="70"/>
-      <c r="G57" s="70"/>
-      <c r="H57" s="11"/>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A58" s="11"/>
-      <c r="B58" s="70"/>
-      <c r="C58" s="70"/>
-      <c r="D58" s="70"/>
-      <c r="E58" s="70"/>
-      <c r="F58" s="70"/>
-      <c r="G58" s="70"/>
-      <c r="H58" s="11"/>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A59" s="11"/>
-      <c r="B59" s="70"/>
-      <c r="C59" s="70"/>
-      <c r="D59" s="70"/>
-      <c r="E59" s="70"/>
-      <c r="F59" s="70"/>
-      <c r="G59" s="70"/>
-      <c r="H59" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B54:G59"/>
-    <mergeCell ref="A43:H44"/>
-    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="B50:G55"/>
+    <mergeCell ref="A39:H40"/>
+    <mergeCell ref="A42:H42"/>
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A27:H27"/>
     <mergeCell ref="A30:H30"/>
-    <mergeCell ref="A34:H34"/>
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A25:G25"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>

--- a/FLORES DE ESTRADA/Mayo/RESUMEN-MAYO-ESTRADA.xlsx
+++ b/FLORES DE ESTRADA/Mayo/RESUMEN-MAYO-ESTRADA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A23BAE0C-CC29-4A6B-B71E-3827556D7DE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15E7EAC1-4C1D-42CE-9145-18144AEEC623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$1:$H$56</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$1:$H$55</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
   <si>
     <t>Domicilio:</t>
   </si>
@@ -105,9 +105,6 @@
     <t>TOTAL DE GASTOS ORDINARIOS 1,2,4,5,6;</t>
   </si>
   <si>
-    <t>TOTAL GASTOS EXTRAORD</t>
-  </si>
-  <si>
     <t>MP 1148</t>
   </si>
   <si>
@@ -163,6 +160,12 @@
   </si>
   <si>
     <t>CAJA NO REAL, YA QUE DE ESTE FONDO SE PAGA EDESUR DE LAS UNIDADES FUNCIONALES ATRASADAS. QUIEN SE ATRASE CON EDESUR TENDRA PUNITORIOS.</t>
+  </si>
+  <si>
+    <t>Servisur - mano de obra instalacion reflector</t>
+  </si>
+  <si>
+    <t>Casa ruan compra de reflector, dicroicas y cable unipolar</t>
   </si>
 </sst>
 </file>
@@ -293,18 +296,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="1"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -444,44 +447,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -511,12 +483,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="7" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -533,9 +499,6 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -547,7 +510,14 @@
     <xf numFmtId="166" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -589,10 +559,21 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -930,7 +911,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11.7109375" customWidth="1"/>
@@ -940,20 +921,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="36"/>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="38"/>
+      <c r="A1" s="30"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="32"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="34"/>
+      <c r="A2" s="28"/>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
-      <c r="D2" s="39" t="s">
+      <c r="D2" s="33" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="11" t="s">
@@ -964,10 +945,10 @@
       <c r="H2" s="7"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="34"/>
+      <c r="A3" s="28"/>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
-      <c r="D3" s="39" t="s">
+      <c r="D3" s="33" t="s">
         <v>2</v>
       </c>
       <c r="E3" s="11">
@@ -978,13 +959,13 @@
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="34"/>
+      <c r="A4" s="28"/>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
-      <c r="D4" s="39" t="s">
+      <c r="D4" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="40" t="s">
+      <c r="E4" s="34" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="11"/>
@@ -992,11 +973,11 @@
       <c r="H4" s="7"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="34"/>
+      <c r="A5" s="28"/>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
-      <c r="D5" s="39" t="s">
-        <v>27</v>
+      <c r="D5" s="33" t="s">
+        <v>26</v>
       </c>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
@@ -1004,7 +985,7 @@
       <c r="H5" s="7"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="34"/>
+      <c r="A6" s="28"/>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
@@ -1014,31 +995,31 @@
       <c r="H6" s="7"/>
     </row>
     <row r="7" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A7" s="41" t="s">
+      <c r="A7" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="42"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" s="42"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="44"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="36"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="38"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="36"/>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="38"/>
+      <c r="A8" s="30"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="32"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="28" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="11"/>
@@ -1052,7 +1033,7 @@
       <c r="H9" s="7"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="34" t="s">
+      <c r="A10" s="28" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="11" t="s">
@@ -1076,20 +1057,20 @@
       <c r="H11" s="6"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="64" t="s">
+      <c r="A12" s="58" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="64"/>
-      <c r="C12" s="64"/>
-      <c r="D12" s="64"/>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="64"/>
-      <c r="H12" s="64"/>
+      <c r="B12" s="58"/>
+      <c r="C12" s="58"/>
+      <c r="D12" s="58"/>
+      <c r="E12" s="58"/>
+      <c r="F12" s="58"/>
+      <c r="G12" s="58"/>
+      <c r="H12" s="58"/>
     </row>
     <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="34" t="s">
-        <v>28</v>
+      <c r="A13" s="28" t="s">
+        <v>27</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -1097,54 +1078,54 @@
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="11"/>
-      <c r="H13" s="48">
+      <c r="H13" s="39">
         <v>194000</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="68" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="69"/>
-      <c r="C14" s="69"/>
-      <c r="D14" s="69"/>
-      <c r="E14" s="69"/>
-      <c r="F14" s="69"/>
-      <c r="G14" s="69"/>
-      <c r="H14" s="48">
+      <c r="A14" s="62" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="63"/>
+      <c r="C14" s="63"/>
+      <c r="D14" s="63"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="63"/>
+      <c r="G14" s="63"/>
+      <c r="H14" s="39">
         <v>3567.21</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="49" t="s">
+      <c r="A15" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="50"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="50"/>
-      <c r="E15" s="50"/>
-      <c r="F15" s="50"/>
-      <c r="G15" s="50"/>
-      <c r="H15" s="51">
+      <c r="B15" s="41"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="42">
         <f>SUM(H13:H14)</f>
         <v>197567.21</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="65" t="s">
+      <c r="A16" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="66"/>
-      <c r="C16" s="66"/>
-      <c r="D16" s="66"/>
-      <c r="E16" s="66"/>
-      <c r="F16" s="66"/>
-      <c r="G16" s="66"/>
-      <c r="H16" s="67"/>
+      <c r="B16" s="60"/>
+      <c r="C16" s="60"/>
+      <c r="D16" s="60"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="60"/>
+      <c r="G16" s="60"/>
+      <c r="H16" s="61"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="34" t="s">
-        <v>37</v>
+      <c r="A17" s="28" t="s">
+        <v>36</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -1152,54 +1133,54 @@
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
       <c r="G17" s="11"/>
-      <c r="H17" s="52">
+      <c r="H17" s="43">
         <v>29660.67</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="49" t="s">
+      <c r="A18" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="50"/>
-      <c r="C18" s="50"/>
-      <c r="D18" s="50"/>
-      <c r="E18" s="50"/>
-      <c r="F18" s="50"/>
-      <c r="G18" s="50"/>
-      <c r="H18" s="53">
+      <c r="B18" s="41"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="44">
         <f>SUM(H17:H17)</f>
         <v>29660.67</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="65" t="s">
+      <c r="A19" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="66"/>
-      <c r="C19" s="66"/>
-      <c r="D19" s="66"/>
-      <c r="E19" s="66"/>
-      <c r="F19" s="66"/>
-      <c r="G19" s="66"/>
-      <c r="H19" s="67"/>
+      <c r="B19" s="60"/>
+      <c r="C19" s="60"/>
+      <c r="D19" s="60"/>
+      <c r="E19" s="60"/>
+      <c r="F19" s="60"/>
+      <c r="G19" s="60"/>
+      <c r="H19" s="61"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="54" t="s">
+      <c r="A20" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="55"/>
-      <c r="C20" s="55"/>
-      <c r="D20" s="55"/>
-      <c r="E20" s="55"/>
-      <c r="F20" s="55"/>
-      <c r="G20" s="55"/>
-      <c r="H20" s="56">
+      <c r="B20" s="46"/>
+      <c r="C20" s="46"/>
+      <c r="D20" s="46"/>
+      <c r="E20" s="46"/>
+      <c r="F20" s="46"/>
+      <c r="G20" s="46"/>
+      <c r="H20" s="47">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="34" t="s">
-        <v>33</v>
+      <c r="A21" s="28" t="s">
+        <v>32</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -1207,12 +1188,12 @@
       <c r="E21" s="11"/>
       <c r="F21" s="11"/>
       <c r="G21" s="11"/>
-      <c r="H21" s="52">
+      <c r="H21" s="43">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="34" t="s">
+      <c r="A22" s="28" t="s">
         <v>9</v>
       </c>
       <c r="B22" s="11"/>
@@ -1221,55 +1202,54 @@
       <c r="E22" s="11"/>
       <c r="F22" s="11"/>
       <c r="G22" s="11"/>
-      <c r="H22" s="57">
+      <c r="H22" s="48">
         <f>SUM(H20:H21)</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="64" t="s">
+      <c r="A23" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="64"/>
-      <c r="C23" s="64"/>
-      <c r="D23" s="64"/>
-      <c r="E23" s="64"/>
-      <c r="F23" s="64"/>
-      <c r="G23" s="64"/>
-      <c r="H23" s="64"/>
+      <c r="B23" s="58"/>
+      <c r="C23" s="58"/>
+      <c r="D23" s="58"/>
+      <c r="E23" s="58"/>
+      <c r="F23" s="58"/>
+      <c r="G23" s="58"/>
+      <c r="H23" s="58"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="70" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="71"/>
-      <c r="C24" s="71"/>
-      <c r="D24" s="71"/>
-      <c r="E24" s="71"/>
-      <c r="F24" s="71"/>
-      <c r="G24" s="71"/>
-      <c r="H24" s="52">
+      <c r="A24" s="64" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="65"/>
+      <c r="C24" s="65"/>
+      <c r="D24" s="65"/>
+      <c r="E24" s="65"/>
+      <c r="F24" s="65"/>
+      <c r="G24" s="65"/>
+      <c r="H24" s="43">
         <v>91930.94</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="72" t="s">
-        <v>43</v>
-      </c>
-      <c r="B25" s="73"/>
-      <c r="C25" s="73"/>
-      <c r="D25" s="73"/>
-      <c r="E25" s="73"/>
-      <c r="F25" s="73"/>
-      <c r="G25" s="73"/>
-      <c r="H25" s="52">
-        <f>167000+70000</f>
-        <v>237000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="49" t="s">
-        <v>12</v>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="51" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" s="50"/>
+      <c r="C25" s="50"/>
+      <c r="D25" s="50"/>
+      <c r="E25" s="50"/>
+      <c r="F25" s="50"/>
+      <c r="G25" s="50"/>
+      <c r="H25" s="43">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="51" t="s">
+        <v>45</v>
       </c>
       <c r="B26" s="50"/>
       <c r="C26" s="50"/>
@@ -1277,236 +1257,249 @@
       <c r="E26" s="50"/>
       <c r="F26" s="50"/>
       <c r="G26" s="50"/>
-      <c r="H26" s="53">
-        <f>SUM(H24:H25)</f>
-        <v>328930.94</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="65" t="s">
+      <c r="H26" s="43">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="66" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" s="67"/>
+      <c r="C27" s="67"/>
+      <c r="D27" s="67"/>
+      <c r="E27" s="67"/>
+      <c r="F27" s="67"/>
+      <c r="G27" s="67"/>
+      <c r="H27" s="43">
+        <f>167000+70000</f>
+        <v>237000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" s="41"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="41"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="44">
+        <f>SUM(H24:H27)</f>
+        <v>385430.94</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="B27" s="66"/>
-      <c r="C27" s="66"/>
-      <c r="D27" s="66"/>
-      <c r="E27" s="66"/>
-      <c r="F27" s="66"/>
-      <c r="G27" s="66"/>
-      <c r="H27" s="67"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="34" t="s">
+      <c r="B29" s="60"/>
+      <c r="C29" s="60"/>
+      <c r="D29" s="60"/>
+      <c r="E29" s="60"/>
+      <c r="F29" s="60"/>
+      <c r="G29" s="60"/>
+      <c r="H29" s="61"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11" t="s">
+      <c r="B30" s="11"/>
+      <c r="C30" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="F28" s="11"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="32"/>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="49" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="50"/>
-      <c r="C29" s="50"/>
-      <c r="D29" s="50"/>
-      <c r="E29" s="50"/>
-      <c r="F29" s="50"/>
-      <c r="G29" s="50"/>
-      <c r="H29" s="74">
+      <c r="D30" s="11"/>
+      <c r="E30" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="26"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="41"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="41"/>
+      <c r="H31" s="52">
         <v>139770.16</v>
       </c>
-      <c r="I29" s="32"/>
-      <c r="K29" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="64" t="s">
+      <c r="I31" s="26"/>
+      <c r="K31" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="58" t="s">
         <v>23</v>
       </c>
-      <c r="B30" s="64"/>
-      <c r="C30" s="64"/>
-      <c r="D30" s="64"/>
-      <c r="E30" s="64"/>
-      <c r="F30" s="64"/>
-      <c r="G30" s="64"/>
-      <c r="H30" s="64"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="58">
+      <c r="B32" s="58"/>
+      <c r="C32" s="58"/>
+      <c r="D32" s="58"/>
+      <c r="E32" s="58"/>
+      <c r="F32" s="58"/>
+      <c r="G32" s="58"/>
+      <c r="H32" s="58"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="49">
         <v>49773</v>
       </c>
     </row>
-    <row r="32" spans="1:11" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="8" t="s">
+    <row r="34" spans="1:10" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="10">
-        <f>H31+H29+H26+H22+H18+H15</f>
-        <v>745701.98</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="B33" s="21"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="22">
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="10">
+        <f>H33+H31+H28+H22+H18+H15</f>
+        <v>802201.98</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="22">
         <v>500000</v>
       </c>
-      <c r="I33" s="33"/>
-      <c r="J33" s="33"/>
-    </row>
-    <row r="34" spans="1:10" s="3" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B34" s="21"/>
-      <c r="C34" s="21"/>
-      <c r="D34" s="21"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="21"/>
-      <c r="G34" s="21"/>
-      <c r="H34" s="22">
-        <f>H32+H33</f>
-        <v>1245701.98</v>
-      </c>
-      <c r="I34" s="35"/>
-    </row>
-    <row r="35" spans="1:10" s="3" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="23"/>
-      <c r="B35" s="24"/>
-      <c r="C35" s="24"/>
-      <c r="D35" s="24"/>
-      <c r="E35" s="24"/>
-      <c r="F35" s="24"/>
-      <c r="G35" s="24"/>
-      <c r="H35" s="25"/>
+      <c r="I35" s="27"/>
+      <c r="J35" s="27"/>
     </row>
     <row r="36" spans="1:10" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="26"/>
-      <c r="B36" s="26"/>
-      <c r="C36" s="26"/>
-      <c r="D36" s="26"/>
-      <c r="E36" s="26"/>
-      <c r="F36" s="26"/>
-      <c r="G36" s="26"/>
-      <c r="H36" s="27"/>
-    </row>
-    <row r="37" spans="1:10" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="26"/>
-      <c r="B37" s="26"/>
-      <c r="C37" s="26"/>
-      <c r="D37" s="26"/>
-      <c r="E37" s="26"/>
-      <c r="F37" s="26"/>
-      <c r="G37" s="26"/>
-      <c r="H37" s="28"/>
-    </row>
-    <row r="38" spans="1:10" s="1" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="45" t="s">
-        <v>25</v>
-      </c>
-      <c r="B38" s="46"/>
-      <c r="C38" s="46"/>
-      <c r="D38" s="46"/>
-      <c r="E38" s="46"/>
-      <c r="F38" s="46"/>
-      <c r="G38" s="46"/>
-      <c r="H38" s="47">
-        <f>SUM(H36:H37)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="60" t="s">
+      <c r="A36" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B36" s="21"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="22">
+        <f>H34+H35</f>
+        <v>1302201.98</v>
+      </c>
+      <c r="I36" s="29"/>
+    </row>
+    <row r="37" spans="1:10" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="69" t="str">
+        <f>UPPER("Prevision Extraordinaria")</f>
+        <v>PREVISION EXTRAORDINARIA</v>
+      </c>
+      <c r="B37" s="70"/>
+      <c r="C37" s="70"/>
+      <c r="D37" s="70"/>
+      <c r="E37" s="70"/>
+      <c r="F37" s="70"/>
+      <c r="G37" s="71"/>
+      <c r="H37" s="68">
+        <v>700000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="B39" s="60"/>
-      <c r="C39" s="60"/>
-      <c r="D39" s="60"/>
-      <c r="E39" s="60"/>
-      <c r="F39" s="60"/>
-      <c r="G39" s="60"/>
-      <c r="H39" s="60"/>
-    </row>
-    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="60"/>
-      <c r="B40" s="60"/>
-      <c r="C40" s="60"/>
-      <c r="D40" s="60"/>
-      <c r="E40" s="60"/>
-      <c r="F40" s="60"/>
-      <c r="G40" s="60"/>
-      <c r="H40" s="60"/>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="11"/>
-      <c r="B41" s="11"/>
-      <c r="C41" s="11"/>
-      <c r="D41" s="11"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="11"/>
+      <c r="B38" s="54"/>
+      <c r="C38" s="54"/>
+      <c r="D38" s="54"/>
+      <c r="E38" s="54"/>
+      <c r="F38" s="54"/>
+      <c r="G38" s="54"/>
+      <c r="H38" s="54"/>
+    </row>
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="54"/>
+      <c r="B39" s="54"/>
+      <c r="C39" s="54"/>
+      <c r="D39" s="54"/>
+      <c r="E39" s="54"/>
+      <c r="F39" s="54"/>
+      <c r="G39" s="54"/>
+      <c r="H39" s="54"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="11"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="11"/>
+    </row>
+    <row r="41" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A41" s="55"/>
+      <c r="B41" s="56"/>
+      <c r="C41" s="56"/>
+      <c r="D41" s="56"/>
+      <c r="E41" s="56"/>
+      <c r="F41" s="56"/>
+      <c r="G41" s="56"/>
+      <c r="H41" s="57"/>
+      <c r="J41" s="2"/>
     </row>
     <row r="42" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A42" s="61"/>
-      <c r="B42" s="62"/>
-      <c r="C42" s="62"/>
-      <c r="D42" s="62"/>
-      <c r="E42" s="62"/>
-      <c r="F42" s="62"/>
-      <c r="G42" s="62"/>
-      <c r="H42" s="63"/>
-      <c r="J42" s="2"/>
-    </row>
-    <row r="43" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A43" s="12" t="s">
+      <c r="A42" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B43" s="13"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="13"/>
-      <c r="H43" s="20">
+      <c r="B42" s="13"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
+      <c r="H42" s="20">
         <v>1495376.39</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B43" s="15"/>
+      <c r="C43" s="15"/>
+      <c r="D43" s="15"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="15"/>
+      <c r="G43" s="15"/>
+      <c r="H43" s="24">
+        <v>1264656.6683125077</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="14" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B44" s="15"/>
       <c r="C44" s="15"/>
@@ -1514,13 +1507,12 @@
       <c r="E44" s="15"/>
       <c r="F44" s="15"/>
       <c r="G44" s="15"/>
-      <c r="H44" s="30">
-        <v>1027656.6683125072</v>
-      </c>
+      <c r="H44" s="16"/>
+      <c r="I44" s="25"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="14" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B45" s="15"/>
       <c r="C45" s="15"/>
@@ -1528,8 +1520,10 @@
       <c r="E45" s="15"/>
       <c r="F45" s="15"/>
       <c r="G45" s="15"/>
-      <c r="H45" s="16"/>
-      <c r="I45" s="31"/>
+      <c r="H45" s="17">
+        <f>-( H34 )</f>
+        <v>-802201.98</v>
+      </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="14" t="s">
@@ -1541,124 +1535,110 @@
       <c r="E46" s="15"/>
       <c r="F46" s="15"/>
       <c r="G46" s="15"/>
-      <c r="H46" s="17">
-        <f>-( H32 )</f>
-        <v>-745701.98</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="15"/>
-      <c r="C47" s="15"/>
-      <c r="D47" s="15"/>
-      <c r="E47" s="15"/>
-      <c r="F47" s="15"/>
-      <c r="G47" s="15"/>
-      <c r="H47" s="17"/>
-    </row>
-    <row r="48" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A48" s="18" t="s">
+      <c r="H46" s="17"/>
+    </row>
+    <row r="47" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A47" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B48" s="19"/>
-      <c r="C48" s="19"/>
-      <c r="D48" s="19"/>
-      <c r="E48" s="19"/>
-      <c r="F48" s="19"/>
-      <c r="G48" s="19"/>
-      <c r="H48" s="29">
-        <f>SUM(H43:H47)</f>
-        <v>1777331.0783125074</v>
-      </c>
+      <c r="B47" s="19"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="19"/>
+      <c r="F47" s="19"/>
+      <c r="G47" s="19"/>
+      <c r="H47" s="23">
+        <f>SUM(H42:H46)</f>
+        <v>1957831.0783125074</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="11"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="11"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="11"/>
-      <c r="B49" s="11"/>
-      <c r="C49" s="11"/>
-      <c r="D49" s="11"/>
-      <c r="E49" s="11"/>
-      <c r="F49" s="11"/>
-      <c r="G49" s="11"/>
+      <c r="B49" s="53" t="s">
+        <v>43</v>
+      </c>
+      <c r="C49" s="53"/>
+      <c r="D49" s="53"/>
+      <c r="E49" s="53"/>
+      <c r="F49" s="53"/>
+      <c r="G49" s="53"/>
       <c r="H49" s="11"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="11"/>
-      <c r="B50" s="59" t="s">
-        <v>44</v>
-      </c>
-      <c r="C50" s="59"/>
-      <c r="D50" s="59"/>
-      <c r="E50" s="59"/>
-      <c r="F50" s="59"/>
-      <c r="G50" s="59"/>
+      <c r="B50" s="53"/>
+      <c r="C50" s="53"/>
+      <c r="D50" s="53"/>
+      <c r="E50" s="53"/>
+      <c r="F50" s="53"/>
+      <c r="G50" s="53"/>
       <c r="H50" s="11"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="11"/>
-      <c r="B51" s="59"/>
-      <c r="C51" s="59"/>
-      <c r="D51" s="59"/>
-      <c r="E51" s="59"/>
-      <c r="F51" s="59"/>
-      <c r="G51" s="59"/>
+      <c r="B51" s="53"/>
+      <c r="C51" s="53"/>
+      <c r="D51" s="53"/>
+      <c r="E51" s="53"/>
+      <c r="F51" s="53"/>
+      <c r="G51" s="53"/>
       <c r="H51" s="11"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="11"/>
-      <c r="B52" s="59"/>
-      <c r="C52" s="59"/>
-      <c r="D52" s="59"/>
-      <c r="E52" s="59"/>
-      <c r="F52" s="59"/>
-      <c r="G52" s="59"/>
+      <c r="B52" s="53"/>
+      <c r="C52" s="53"/>
+      <c r="D52" s="53"/>
+      <c r="E52" s="53"/>
+      <c r="F52" s="53"/>
+      <c r="G52" s="53"/>
       <c r="H52" s="11"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="11"/>
-      <c r="B53" s="59"/>
-      <c r="C53" s="59"/>
-      <c r="D53" s="59"/>
-      <c r="E53" s="59"/>
-      <c r="F53" s="59"/>
-      <c r="G53" s="59"/>
+      <c r="B53" s="53"/>
+      <c r="C53" s="53"/>
+      <c r="D53" s="53"/>
+      <c r="E53" s="53"/>
+      <c r="F53" s="53"/>
+      <c r="G53" s="53"/>
       <c r="H53" s="11"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="11"/>
-      <c r="B54" s="59"/>
-      <c r="C54" s="59"/>
-      <c r="D54" s="59"/>
-      <c r="E54" s="59"/>
-      <c r="F54" s="59"/>
-      <c r="G54" s="59"/>
+      <c r="B54" s="53"/>
+      <c r="C54" s="53"/>
+      <c r="D54" s="53"/>
+      <c r="E54" s="53"/>
+      <c r="F54" s="53"/>
+      <c r="G54" s="53"/>
       <c r="H54" s="11"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="11"/>
-      <c r="B55" s="59"/>
-      <c r="C55" s="59"/>
-      <c r="D55" s="59"/>
-      <c r="E55" s="59"/>
-      <c r="F55" s="59"/>
-      <c r="G55" s="59"/>
-      <c r="H55" s="11"/>
-    </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="B50:G55"/>
-    <mergeCell ref="A39:H40"/>
-    <mergeCell ref="A42:H42"/>
+  <mergeCells count="13">
+    <mergeCell ref="B49:G54"/>
+    <mergeCell ref="A38:H39"/>
+    <mergeCell ref="A41:H41"/>
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A32:H32"/>
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A37:G37"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
